--- a/Result/AsignacionTurnos.xlsx
+++ b/Result/AsignacionTurnos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2084"/>
+  <dimension ref="A1:E2091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42082,7 +42082,7 @@
     </row>
     <row r="1667">
       <c r="A1667" t="n">
-        <v>4556212</v>
+        <v>4555531</v>
       </c>
       <c r="B1667" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
     </row>
     <row r="1668">
       <c r="A1668" t="n">
-        <v>4556218</v>
+        <v>4555553</v>
       </c>
       <c r="B1668" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
     </row>
     <row r="1669">
       <c r="A1669" t="n">
-        <v>4556223</v>
+        <v>4555565</v>
       </c>
       <c r="B1669" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
     </row>
     <row r="1670">
       <c r="A1670" t="n">
-        <v>4556234</v>
+        <v>4555572</v>
       </c>
       <c r="B1670" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
     </row>
     <row r="1671">
       <c r="A1671" t="n">
-        <v>4556238</v>
+        <v>4555584</v>
       </c>
       <c r="B1671" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
     </row>
     <row r="1672">
       <c r="A1672" t="n">
-        <v>4556252</v>
+        <v>4555607</v>
       </c>
       <c r="B1672" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
     </row>
     <row r="1673">
       <c r="A1673" t="n">
-        <v>4556256</v>
+        <v>4555653</v>
       </c>
       <c r="B1673" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
     </row>
     <row r="1674">
       <c r="A1674" t="n">
-        <v>4556266</v>
+        <v>4555665</v>
       </c>
       <c r="B1674" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
     </row>
     <row r="1675">
       <c r="A1675" t="n">
-        <v>4556271</v>
+        <v>4555677</v>
       </c>
       <c r="B1675" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
     </row>
     <row r="1676">
       <c r="A1676" t="n">
-        <v>4556272</v>
+        <v>4555680</v>
       </c>
       <c r="B1676" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
     </row>
     <row r="1677">
       <c r="A1677" t="n">
-        <v>4556277</v>
+        <v>4555698</v>
       </c>
       <c r="B1677" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
     </row>
     <row r="1678">
       <c r="A1678" t="n">
-        <v>4556280</v>
+        <v>4555707</v>
       </c>
       <c r="B1678" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
     </row>
     <row r="1679">
       <c r="A1679" t="n">
-        <v>4556282</v>
+        <v>4555721</v>
       </c>
       <c r="B1679" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
     </row>
     <row r="1680">
       <c r="A1680" t="n">
-        <v>4556287</v>
+        <v>4555736</v>
       </c>
       <c r="B1680" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
     </row>
     <row r="1681">
       <c r="A1681" t="n">
-        <v>4556298</v>
+        <v>4555759</v>
       </c>
       <c r="B1681" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
     </row>
     <row r="1682">
       <c r="A1682" t="n">
-        <v>4556306</v>
+        <v>4555784</v>
       </c>
       <c r="B1682" t="inlineStr">
         <is>
@@ -42482,7 +42482,7 @@
     </row>
     <row r="1683">
       <c r="A1683" t="n">
-        <v>4556316</v>
+        <v>4555829</v>
       </c>
       <c r="B1683" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
     </row>
     <row r="1684">
       <c r="A1684" t="n">
-        <v>4556325</v>
+        <v>4555837</v>
       </c>
       <c r="B1684" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
     </row>
     <row r="1685">
       <c r="A1685" t="n">
-        <v>4556330</v>
+        <v>4555843</v>
       </c>
       <c r="B1685" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
     </row>
     <row r="1686">
       <c r="A1686" t="n">
-        <v>4556332</v>
+        <v>4555852</v>
       </c>
       <c r="B1686" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
     </row>
     <row r="1687">
       <c r="A1687" t="n">
-        <v>4556340</v>
+        <v>4555870</v>
       </c>
       <c r="B1687" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
     </row>
     <row r="1688">
       <c r="A1688" t="n">
-        <v>4556341</v>
+        <v>4555886</v>
       </c>
       <c r="B1688" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
     </row>
     <row r="1689">
       <c r="A1689" t="n">
-        <v>4556352</v>
+        <v>4555894</v>
       </c>
       <c r="B1689" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
     </row>
     <row r="1690">
       <c r="A1690" t="n">
-        <v>4556361</v>
+        <v>4555900</v>
       </c>
       <c r="B1690" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
     </row>
     <row r="1691">
       <c r="A1691" t="n">
-        <v>4556371</v>
+        <v>4555916</v>
       </c>
       <c r="B1691" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
     </row>
     <row r="1692">
       <c r="A1692" t="n">
-        <v>4556378</v>
+        <v>4555940</v>
       </c>
       <c r="B1692" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
     </row>
     <row r="1693">
       <c r="A1693" t="n">
-        <v>4556379</v>
+        <v>4555970</v>
       </c>
       <c r="B1693" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
     </row>
     <row r="1694">
       <c r="A1694" t="n">
-        <v>4556382</v>
+        <v>4555993</v>
       </c>
       <c r="B1694" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
     </row>
     <row r="1695">
       <c r="A1695" t="n">
-        <v>4556387</v>
+        <v>4556001</v>
       </c>
       <c r="B1695" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
     </row>
     <row r="1696">
       <c r="A1696" t="n">
-        <v>4556388</v>
+        <v>4556026</v>
       </c>
       <c r="B1696" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
     </row>
     <row r="1697">
       <c r="A1697" t="n">
-        <v>4556389</v>
+        <v>4556027</v>
       </c>
       <c r="B1697" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
     </row>
     <row r="1698">
       <c r="A1698" t="n">
-        <v>4556407</v>
+        <v>4556044</v>
       </c>
       <c r="B1698" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
     </row>
     <row r="1699">
       <c r="A1699" t="n">
-        <v>4556418</v>
+        <v>4556057</v>
       </c>
       <c r="B1699" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
     </row>
     <row r="1700">
       <c r="A1700" t="n">
-        <v>4556427</v>
+        <v>4556064</v>
       </c>
       <c r="B1700" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
     </row>
     <row r="1701">
       <c r="A1701" t="n">
-        <v>4556430</v>
+        <v>4556071</v>
       </c>
       <c r="B1701" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
     </row>
     <row r="1702">
       <c r="A1702" t="n">
-        <v>4556437</v>
+        <v>4556081</v>
       </c>
       <c r="B1702" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
     </row>
     <row r="1703">
       <c r="A1703" t="n">
-        <v>4556446</v>
+        <v>4556087</v>
       </c>
       <c r="B1703" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
     </row>
     <row r="1704">
       <c r="A1704" t="n">
-        <v>4556449</v>
+        <v>4556088</v>
       </c>
       <c r="B1704" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
     </row>
     <row r="1705">
       <c r="A1705" t="n">
-        <v>4556459</v>
+        <v>4556096</v>
       </c>
       <c r="B1705" t="inlineStr">
         <is>
@@ -43057,7 +43057,7 @@
     </row>
     <row r="1706">
       <c r="A1706" t="n">
-        <v>4556469</v>
+        <v>4556100</v>
       </c>
       <c r="B1706" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
     </row>
     <row r="1707">
       <c r="A1707" t="n">
-        <v>4556474</v>
+        <v>4556106</v>
       </c>
       <c r="B1707" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
     </row>
     <row r="1708">
       <c r="A1708" t="n">
-        <v>4556483</v>
+        <v>4556116</v>
       </c>
       <c r="B1708" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
     </row>
     <row r="1709">
       <c r="A1709" t="n">
-        <v>4556487</v>
+        <v>4556122</v>
       </c>
       <c r="B1709" t="inlineStr">
         <is>
@@ -43157,7 +43157,7 @@
     </row>
     <row r="1710">
       <c r="A1710" t="n">
-        <v>4556492</v>
+        <v>4556123</v>
       </c>
       <c r="B1710" t="inlineStr">
         <is>
@@ -43182,7 +43182,7 @@
     </row>
     <row r="1711">
       <c r="A1711" t="n">
-        <v>4556501</v>
+        <v>4556126</v>
       </c>
       <c r="B1711" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
     </row>
     <row r="1712">
       <c r="A1712" t="n">
-        <v>4556508</v>
+        <v>4556131</v>
       </c>
       <c r="B1712" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
     </row>
     <row r="1713">
       <c r="A1713" t="n">
-        <v>4556518</v>
+        <v>4556136</v>
       </c>
       <c r="B1713" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
     </row>
     <row r="1714">
       <c r="A1714" t="n">
-        <v>4556520</v>
+        <v>4556142</v>
       </c>
       <c r="B1714" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
     </row>
     <row r="1715">
       <c r="A1715" t="n">
-        <v>4556530</v>
+        <v>4556150</v>
       </c>
       <c r="B1715" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
     </row>
     <row r="1716">
       <c r="A1716" t="n">
-        <v>4556536</v>
+        <v>4556155</v>
       </c>
       <c r="B1716" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
     </row>
     <row r="1717">
       <c r="A1717" t="n">
-        <v>4556539</v>
+        <v>4556158</v>
       </c>
       <c r="B1717" t="inlineStr">
         <is>
@@ -43357,7 +43357,7 @@
     </row>
     <row r="1718">
       <c r="A1718" t="n">
-        <v>4556546</v>
+        <v>4556170</v>
       </c>
       <c r="B1718" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
     </row>
     <row r="1719">
       <c r="A1719" t="n">
-        <v>4556548</v>
+        <v>4556174</v>
       </c>
       <c r="B1719" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
     </row>
     <row r="1720">
       <c r="A1720" t="n">
-        <v>4556557</v>
+        <v>4556180</v>
       </c>
       <c r="B1720" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
     </row>
     <row r="1721">
       <c r="A1721" t="n">
-        <v>4556567</v>
+        <v>4556182</v>
       </c>
       <c r="B1721" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
     </row>
     <row r="1722">
       <c r="A1722" t="n">
-        <v>4556574</v>
+        <v>4556186</v>
       </c>
       <c r="B1722" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
     </row>
     <row r="1723">
       <c r="A1723" t="n">
-        <v>4556584</v>
+        <v>4556192</v>
       </c>
       <c r="B1723" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
     </row>
     <row r="1724">
       <c r="A1724" t="n">
-        <v>4556585</v>
+        <v>4556198</v>
       </c>
       <c r="B1724" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
     </row>
     <row r="1725">
       <c r="A1725" t="n">
-        <v>4556587</v>
+        <v>4556202</v>
       </c>
       <c r="B1725" t="inlineStr">
         <is>
@@ -43557,7 +43557,7 @@
     </row>
     <row r="1726">
       <c r="A1726" t="n">
-        <v>4556594</v>
+        <v>4556210</v>
       </c>
       <c r="B1726" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
     </row>
     <row r="1727">
       <c r="A1727" t="n">
-        <v>4556596</v>
+        <v>4556212</v>
       </c>
       <c r="B1727" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
     </row>
     <row r="1728">
       <c r="A1728" t="n">
-        <v>4556607</v>
+        <v>4556218</v>
       </c>
       <c r="B1728" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
     </row>
     <row r="1729">
       <c r="A1729" t="n">
-        <v>4556693</v>
+        <v>4556223</v>
       </c>
       <c r="B1729" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
     </row>
     <row r="1730">
       <c r="A1730" t="n">
-        <v>4556702</v>
+        <v>4556234</v>
       </c>
       <c r="B1730" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
     </row>
     <row r="1731">
       <c r="A1731" t="n">
-        <v>4556711</v>
+        <v>4556238</v>
       </c>
       <c r="B1731" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
     </row>
     <row r="1732">
       <c r="A1732" t="n">
-        <v>4556721</v>
+        <v>4556252</v>
       </c>
       <c r="B1732" t="inlineStr">
         <is>
@@ -43732,7 +43732,7 @@
     </row>
     <row r="1733">
       <c r="A1733" t="n">
-        <v>4556725</v>
+        <v>4556256</v>
       </c>
       <c r="B1733" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
     </row>
     <row r="1734">
       <c r="A1734" t="n">
-        <v>4556727</v>
+        <v>4556266</v>
       </c>
       <c r="B1734" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
     </row>
     <row r="1735">
       <c r="A1735" t="n">
-        <v>4556733</v>
+        <v>4556271</v>
       </c>
       <c r="B1735" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
     </row>
     <row r="1736">
       <c r="A1736" t="n">
-        <v>4556738</v>
+        <v>4556272</v>
       </c>
       <c r="B1736" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
     </row>
     <row r="1737">
       <c r="A1737" t="n">
-        <v>4556744</v>
+        <v>4556277</v>
       </c>
       <c r="B1737" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
     </row>
     <row r="1738">
       <c r="A1738" t="n">
-        <v>4556754</v>
+        <v>4556280</v>
       </c>
       <c r="B1738" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
     </row>
     <row r="1739">
       <c r="A1739" t="n">
-        <v>4556609</v>
+        <v>4556282</v>
       </c>
       <c r="B1739" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
     </row>
     <row r="1740">
       <c r="A1740" t="n">
-        <v>4556622</v>
+        <v>4556287</v>
       </c>
       <c r="B1740" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
     </row>
     <row r="1741">
       <c r="A1741" t="n">
-        <v>4556628</v>
+        <v>4556298</v>
       </c>
       <c r="B1741" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
     </row>
     <row r="1742">
       <c r="A1742" t="n">
-        <v>4556629</v>
+        <v>4556306</v>
       </c>
       <c r="B1742" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
     </row>
     <row r="1743">
       <c r="A1743" t="n">
-        <v>4556639</v>
+        <v>4556316</v>
       </c>
       <c r="B1743" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
     </row>
     <row r="1744">
       <c r="A1744" t="n">
-        <v>4556644</v>
+        <v>4556325</v>
       </c>
       <c r="B1744" t="inlineStr">
         <is>
@@ -44032,7 +44032,7 @@
     </row>
     <row r="1745">
       <c r="A1745" t="n">
-        <v>4556645</v>
+        <v>4556330</v>
       </c>
       <c r="B1745" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
     </row>
     <row r="1746">
       <c r="A1746" t="n">
-        <v>4556646</v>
+        <v>4556332</v>
       </c>
       <c r="B1746" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
     </row>
     <row r="1747">
       <c r="A1747" t="n">
-        <v>4556655</v>
+        <v>4556340</v>
       </c>
       <c r="B1747" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
     </row>
     <row r="1748">
       <c r="A1748" t="n">
-        <v>4556664</v>
+        <v>4556341</v>
       </c>
       <c r="B1748" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
     </row>
     <row r="1749">
       <c r="A1749" t="n">
-        <v>4556672</v>
+        <v>4556352</v>
       </c>
       <c r="B1749" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
     </row>
     <row r="1750">
       <c r="A1750" t="n">
-        <v>4556682</v>
+        <v>4556361</v>
       </c>
       <c r="B1750" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
     </row>
     <row r="1751">
       <c r="A1751" t="n">
-        <v>4556688</v>
+        <v>4556371</v>
       </c>
       <c r="B1751" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
     </row>
     <row r="1752">
       <c r="A1752" t="n">
-        <v>4556762</v>
+        <v>4556378</v>
       </c>
       <c r="B1752" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
     </row>
     <row r="1753">
       <c r="A1753" t="n">
-        <v>4556767</v>
+        <v>4556379</v>
       </c>
       <c r="B1753" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
     </row>
     <row r="1754">
       <c r="A1754" t="n">
-        <v>4555531</v>
+        <v>4556382</v>
       </c>
       <c r="B1754" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
     </row>
     <row r="1755">
       <c r="A1755" t="n">
-        <v>4555553</v>
+        <v>4556387</v>
       </c>
       <c r="B1755" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
     </row>
     <row r="1756">
       <c r="A1756" t="n">
-        <v>4555565</v>
+        <v>4556388</v>
       </c>
       <c r="B1756" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
     </row>
     <row r="1757">
       <c r="A1757" t="n">
-        <v>4555572</v>
+        <v>4556389</v>
       </c>
       <c r="B1757" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
     </row>
     <row r="1758">
       <c r="A1758" t="n">
-        <v>4555584</v>
+        <v>4556407</v>
       </c>
       <c r="B1758" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
     </row>
     <row r="1759">
       <c r="A1759" t="n">
-        <v>4555607</v>
+        <v>4556418</v>
       </c>
       <c r="B1759" t="inlineStr">
         <is>
@@ -44407,7 +44407,7 @@
     </row>
     <row r="1760">
       <c r="A1760" t="n">
-        <v>4555653</v>
+        <v>4556427</v>
       </c>
       <c r="B1760" t="inlineStr">
         <is>
@@ -44432,7 +44432,7 @@
     </row>
     <row r="1761">
       <c r="A1761" t="n">
-        <v>4555665</v>
+        <v>4556430</v>
       </c>
       <c r="B1761" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
     </row>
     <row r="1762">
       <c r="A1762" t="n">
-        <v>4555677</v>
+        <v>4556437</v>
       </c>
       <c r="B1762" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
     </row>
     <row r="1763">
       <c r="A1763" t="n">
-        <v>4555680</v>
+        <v>4556446</v>
       </c>
       <c r="B1763" t="inlineStr">
         <is>
@@ -44507,7 +44507,7 @@
     </row>
     <row r="1764">
       <c r="A1764" t="n">
-        <v>4555698</v>
+        <v>4556449</v>
       </c>
       <c r="B1764" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
     </row>
     <row r="1765">
       <c r="A1765" t="n">
-        <v>4555707</v>
+        <v>4556459</v>
       </c>
       <c r="B1765" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
     </row>
     <row r="1766">
       <c r="A1766" t="n">
-        <v>4555721</v>
+        <v>4556469</v>
       </c>
       <c r="B1766" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
     </row>
     <row r="1767">
       <c r="A1767" t="n">
-        <v>4555736</v>
+        <v>4556474</v>
       </c>
       <c r="B1767" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
     </row>
     <row r="1768">
       <c r="A1768" t="n">
-        <v>4555759</v>
+        <v>4556483</v>
       </c>
       <c r="B1768" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
     </row>
     <row r="1769">
       <c r="A1769" t="n">
-        <v>4555784</v>
+        <v>4556487</v>
       </c>
       <c r="B1769" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
     </row>
     <row r="1770">
       <c r="A1770" t="n">
-        <v>4555829</v>
+        <v>4556492</v>
       </c>
       <c r="B1770" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
     </row>
     <row r="1771">
       <c r="A1771" t="n">
-        <v>4555837</v>
+        <v>4556501</v>
       </c>
       <c r="B1771" t="inlineStr">
         <is>
@@ -44707,7 +44707,7 @@
     </row>
     <row r="1772">
       <c r="A1772" t="n">
-        <v>4555843</v>
+        <v>4556508</v>
       </c>
       <c r="B1772" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
     </row>
     <row r="1773">
       <c r="A1773" t="n">
-        <v>4555852</v>
+        <v>4556518</v>
       </c>
       <c r="B1773" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
     </row>
     <row r="1774">
       <c r="A1774" t="n">
-        <v>4555870</v>
+        <v>4556520</v>
       </c>
       <c r="B1774" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
     </row>
     <row r="1775">
       <c r="A1775" t="n">
-        <v>4555886</v>
+        <v>4556530</v>
       </c>
       <c r="B1775" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
     </row>
     <row r="1776">
       <c r="A1776" t="n">
-        <v>4555894</v>
+        <v>4556536</v>
       </c>
       <c r="B1776" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
     </row>
     <row r="1777">
       <c r="A1777" t="n">
-        <v>4555900</v>
+        <v>4556539</v>
       </c>
       <c r="B1777" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
     </row>
     <row r="1778">
       <c r="A1778" t="n">
-        <v>4555916</v>
+        <v>4556546</v>
       </c>
       <c r="B1778" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
     </row>
     <row r="1779">
       <c r="A1779" t="n">
-        <v>4555940</v>
+        <v>4556548</v>
       </c>
       <c r="B1779" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
     </row>
     <row r="1780">
       <c r="A1780" t="n">
-        <v>4555970</v>
+        <v>4556557</v>
       </c>
       <c r="B1780" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
     </row>
     <row r="1781">
       <c r="A1781" t="n">
-        <v>4555993</v>
+        <v>4556567</v>
       </c>
       <c r="B1781" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
     </row>
     <row r="1782">
       <c r="A1782" t="n">
-        <v>4556001</v>
+        <v>4556574</v>
       </c>
       <c r="B1782" t="inlineStr">
         <is>
@@ -44982,7 +44982,7 @@
     </row>
     <row r="1783">
       <c r="A1783" t="n">
-        <v>4556026</v>
+        <v>4556584</v>
       </c>
       <c r="B1783" t="inlineStr">
         <is>
@@ -45007,7 +45007,7 @@
     </row>
     <row r="1784">
       <c r="A1784" t="n">
-        <v>4556769</v>
+        <v>4556585</v>
       </c>
       <c r="B1784" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
     </row>
     <row r="1785">
       <c r="A1785" t="n">
-        <v>4556772</v>
+        <v>4556587</v>
       </c>
       <c r="B1785" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
     </row>
     <row r="1786">
       <c r="A1786" t="n">
-        <v>4556778</v>
+        <v>4556594</v>
       </c>
       <c r="B1786" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
     </row>
     <row r="1787">
       <c r="A1787" t="n">
-        <v>4556788</v>
+        <v>4556596</v>
       </c>
       <c r="B1787" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
     </row>
     <row r="1788">
       <c r="A1788" t="n">
-        <v>4556798</v>
+        <v>4556607</v>
       </c>
       <c r="B1788" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
     </row>
     <row r="1789">
       <c r="A1789" t="n">
-        <v>4556807</v>
+        <v>4556609</v>
       </c>
       <c r="B1789" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
     </row>
     <row r="1790">
       <c r="A1790" t="n">
-        <v>4556809</v>
+        <v>4556622</v>
       </c>
       <c r="B1790" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
     </row>
     <row r="1791">
       <c r="A1791" t="n">
-        <v>4556816</v>
+        <v>4556628</v>
       </c>
       <c r="B1791" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
     </row>
     <row r="1792">
       <c r="A1792" t="n">
-        <v>4556823</v>
+        <v>4556629</v>
       </c>
       <c r="B1792" t="inlineStr">
         <is>
@@ -45232,7 +45232,7 @@
     </row>
     <row r="1793">
       <c r="A1793" t="n">
-        <v>4556831</v>
+        <v>4556639</v>
       </c>
       <c r="B1793" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
     </row>
     <row r="1794">
       <c r="A1794" t="n">
-        <v>4556835</v>
+        <v>4556644</v>
       </c>
       <c r="B1794" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
     </row>
     <row r="1795">
       <c r="A1795" t="n">
-        <v>4556839</v>
+        <v>4556645</v>
       </c>
       <c r="B1795" t="inlineStr">
         <is>
@@ -45307,7 +45307,7 @@
     </row>
     <row r="1796">
       <c r="A1796" t="n">
-        <v>4556844</v>
+        <v>4556646</v>
       </c>
       <c r="B1796" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
     </row>
     <row r="1797">
       <c r="A1797" t="n">
-        <v>4556849</v>
+        <v>4556655</v>
       </c>
       <c r="B1797" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
     </row>
     <row r="1798">
       <c r="A1798" t="n">
-        <v>4556851</v>
+        <v>4556664</v>
       </c>
       <c r="B1798" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
     </row>
     <row r="1799">
       <c r="A1799" t="n">
-        <v>4556858</v>
+        <v>4556672</v>
       </c>
       <c r="B1799" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
     </row>
     <row r="1800">
       <c r="A1800" t="n">
-        <v>4556863</v>
+        <v>4556682</v>
       </c>
       <c r="B1800" t="inlineStr">
         <is>
@@ -45432,7 +45432,7 @@
     </row>
     <row r="1801">
       <c r="A1801" t="n">
-        <v>4556868</v>
+        <v>4556688</v>
       </c>
       <c r="B1801" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
     </row>
     <row r="1802">
       <c r="A1802" t="n">
-        <v>4556873</v>
+        <v>4556693</v>
       </c>
       <c r="B1802" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
     </row>
     <row r="1803">
       <c r="A1803" t="n">
-        <v>4556882</v>
+        <v>4556702</v>
       </c>
       <c r="B1803" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
     </row>
     <row r="1804">
       <c r="A1804" t="n">
-        <v>4556886</v>
+        <v>4556711</v>
       </c>
       <c r="B1804" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
     </row>
     <row r="1805">
       <c r="A1805" t="n">
-        <v>4556893</v>
+        <v>4556721</v>
       </c>
       <c r="B1805" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
     </row>
     <row r="1806">
       <c r="A1806" t="n">
-        <v>4556902</v>
+        <v>4556725</v>
       </c>
       <c r="B1806" t="inlineStr">
         <is>
@@ -45582,7 +45582,7 @@
     </row>
     <row r="1807">
       <c r="A1807" t="n">
-        <v>4556907</v>
+        <v>4556727</v>
       </c>
       <c r="B1807" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
     </row>
     <row r="1808">
       <c r="A1808" t="n">
-        <v>4556917</v>
+        <v>4556733</v>
       </c>
       <c r="B1808" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
     </row>
     <row r="1809">
       <c r="A1809" t="n">
-        <v>4556922</v>
+        <v>4556738</v>
       </c>
       <c r="B1809" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
     </row>
     <row r="1810">
       <c r="A1810" t="n">
-        <v>4556926</v>
+        <v>4556744</v>
       </c>
       <c r="B1810" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
     </row>
     <row r="1811">
       <c r="A1811" t="n">
-        <v>4556929</v>
+        <v>4556754</v>
       </c>
       <c r="B1811" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
     </row>
     <row r="1812">
       <c r="A1812" t="n">
-        <v>4556934</v>
+        <v>4556762</v>
       </c>
       <c r="B1812" t="inlineStr">
         <is>
@@ -45732,7 +45732,7 @@
     </row>
     <row r="1813">
       <c r="A1813" t="n">
-        <v>4556938</v>
+        <v>4556767</v>
       </c>
       <c r="B1813" t="inlineStr">
         <is>
@@ -45757,7 +45757,7 @@
     </row>
     <row r="1814">
       <c r="A1814" t="n">
-        <v>4556939</v>
+        <v>4556769</v>
       </c>
       <c r="B1814" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
     </row>
     <row r="1815">
       <c r="A1815" t="n">
-        <v>4556947</v>
+        <v>4556772</v>
       </c>
       <c r="B1815" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
     </row>
     <row r="1816">
       <c r="A1816" t="n">
-        <v>4556957</v>
+        <v>4556778</v>
       </c>
       <c r="B1816" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
     </row>
     <row r="1817">
       <c r="A1817" t="n">
-        <v>4556971</v>
+        <v>4556788</v>
       </c>
       <c r="B1817" t="inlineStr">
         <is>
@@ -45857,7 +45857,7 @@
     </row>
     <row r="1818">
       <c r="A1818" t="n">
-        <v>4556981</v>
+        <v>4556798</v>
       </c>
       <c r="B1818" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
     </row>
     <row r="1819">
       <c r="A1819" t="n">
-        <v>4556990</v>
+        <v>4556807</v>
       </c>
       <c r="B1819" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
     </row>
     <row r="1820">
       <c r="A1820" t="n">
-        <v>4556999</v>
+        <v>4556809</v>
       </c>
       <c r="B1820" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
     </row>
     <row r="1821">
       <c r="A1821" t="n">
-        <v>4557003</v>
+        <v>4556816</v>
       </c>
       <c r="B1821" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
     </row>
     <row r="1822">
       <c r="A1822" t="n">
-        <v>4557007</v>
+        <v>4556823</v>
       </c>
       <c r="B1822" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
     </row>
     <row r="1823">
       <c r="A1823" t="n">
-        <v>4557017</v>
+        <v>4556831</v>
       </c>
       <c r="B1823" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
     </row>
     <row r="1824">
       <c r="A1824" t="n">
-        <v>4557025</v>
+        <v>4556835</v>
       </c>
       <c r="B1824" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
     </row>
     <row r="1825">
       <c r="A1825" t="n">
-        <v>4557035</v>
+        <v>4556839</v>
       </c>
       <c r="B1825" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
     </row>
     <row r="1826">
       <c r="A1826" t="n">
-        <v>4557043</v>
+        <v>4556844</v>
       </c>
       <c r="B1826" t="inlineStr">
         <is>
@@ -46082,7 +46082,7 @@
     </row>
     <row r="1827">
       <c r="A1827" t="n">
-        <v>4557046</v>
+        <v>4556849</v>
       </c>
       <c r="B1827" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
     </row>
     <row r="1828">
       <c r="A1828" t="n">
-        <v>4557056</v>
+        <v>4556851</v>
       </c>
       <c r="B1828" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
     </row>
     <row r="1829">
       <c r="A1829" t="n">
-        <v>4557065</v>
+        <v>4556858</v>
       </c>
       <c r="B1829" t="inlineStr">
         <is>
@@ -46157,7 +46157,7 @@
     </row>
     <row r="1830">
       <c r="A1830" t="n">
-        <v>4557073</v>
+        <v>4556863</v>
       </c>
       <c r="B1830" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
     </row>
     <row r="1831">
       <c r="A1831" t="n">
-        <v>4557080</v>
+        <v>4556868</v>
       </c>
       <c r="B1831" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
     </row>
     <row r="1832">
       <c r="A1832" t="n">
-        <v>4557084</v>
+        <v>4556873</v>
       </c>
       <c r="B1832" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
     </row>
     <row r="1833">
       <c r="A1833" t="n">
-        <v>4557085</v>
+        <v>4556882</v>
       </c>
       <c r="B1833" t="inlineStr">
         <is>
@@ -46257,7 +46257,7 @@
     </row>
     <row r="1834">
       <c r="A1834" t="n">
-        <v>4557095</v>
+        <v>4556886</v>
       </c>
       <c r="B1834" t="inlineStr">
         <is>
@@ -46282,7 +46282,7 @@
     </row>
     <row r="1835">
       <c r="A1835" t="n">
-        <v>4557098</v>
+        <v>4556893</v>
       </c>
       <c r="B1835" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
     </row>
     <row r="1836">
       <c r="A1836" t="n">
-        <v>4557105</v>
+        <v>4556902</v>
       </c>
       <c r="B1836" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
     </row>
     <row r="1837">
       <c r="A1837" t="n">
-        <v>4557111</v>
+        <v>4556907</v>
       </c>
       <c r="B1837" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
     </row>
     <row r="1838">
       <c r="A1838" t="n">
-        <v>4557121</v>
+        <v>4556917</v>
       </c>
       <c r="B1838" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
     </row>
     <row r="1839">
       <c r="A1839" t="n">
-        <v>4557131</v>
+        <v>4556922</v>
       </c>
       <c r="B1839" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
     </row>
     <row r="1840">
       <c r="A1840" t="n">
-        <v>4557132</v>
+        <v>4556926</v>
       </c>
       <c r="B1840" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
     </row>
     <row r="1841">
       <c r="A1841" t="n">
-        <v>4557135</v>
+        <v>4556929</v>
       </c>
       <c r="B1841" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
     </row>
     <row r="1842">
       <c r="A1842" t="n">
-        <v>4557138</v>
+        <v>4556934</v>
       </c>
       <c r="B1842" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
     </row>
     <row r="1843">
       <c r="A1843" t="n">
-        <v>4557142</v>
+        <v>4556938</v>
       </c>
       <c r="B1843" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
     </row>
     <row r="1844">
       <c r="A1844" t="n">
-        <v>4557143</v>
+        <v>4556939</v>
       </c>
       <c r="B1844" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
     </row>
     <row r="1845">
       <c r="A1845" t="n">
-        <v>4557146</v>
+        <v>4556947</v>
       </c>
       <c r="B1845" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
     </row>
     <row r="1846">
       <c r="A1846" t="n">
-        <v>4557154</v>
+        <v>4556957</v>
       </c>
       <c r="B1846" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
     </row>
     <row r="1847">
       <c r="A1847" t="n">
-        <v>4557158</v>
+        <v>4556971</v>
       </c>
       <c r="B1847" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
     </row>
     <row r="1848">
       <c r="A1848" t="n">
-        <v>4557175</v>
+        <v>4556981</v>
       </c>
       <c r="B1848" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
     </row>
     <row r="1849">
       <c r="A1849" t="n">
-        <v>4557191</v>
+        <v>4556990</v>
       </c>
       <c r="B1849" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
     </row>
     <row r="1850">
       <c r="A1850" t="n">
-        <v>4557192</v>
+        <v>4556999</v>
       </c>
       <c r="B1850" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
     </row>
     <row r="1851">
       <c r="A1851" t="n">
-        <v>4557196</v>
+        <v>4557003</v>
       </c>
       <c r="B1851" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
     </row>
     <row r="1852">
       <c r="A1852" t="n">
-        <v>4557204</v>
+        <v>4557007</v>
       </c>
       <c r="B1852" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
     </row>
     <row r="1853">
       <c r="A1853" t="n">
-        <v>4557208</v>
+        <v>4557017</v>
       </c>
       <c r="B1853" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
     </row>
     <row r="1854">
       <c r="A1854" t="n">
-        <v>4557212</v>
+        <v>4557025</v>
       </c>
       <c r="B1854" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
     </row>
     <row r="1855">
       <c r="A1855" t="n">
-        <v>4557221</v>
+        <v>4557035</v>
       </c>
       <c r="B1855" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
     </row>
     <row r="1856">
       <c r="A1856" t="n">
-        <v>4557231</v>
+        <v>4557043</v>
       </c>
       <c r="B1856" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
     </row>
     <row r="1857">
       <c r="A1857" t="n">
-        <v>4557240</v>
+        <v>4557046</v>
       </c>
       <c r="B1857" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
     </row>
     <row r="1858">
       <c r="A1858" t="n">
-        <v>4557243</v>
+        <v>4557056</v>
       </c>
       <c r="B1858" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
     </row>
     <row r="1859">
       <c r="A1859" t="n">
-        <v>4557252</v>
+        <v>4557065</v>
       </c>
       <c r="B1859" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
     </row>
     <row r="1860">
       <c r="A1860" t="n">
-        <v>4557271</v>
+        <v>4557073</v>
       </c>
       <c r="B1860" t="inlineStr">
         <is>
@@ -46932,7 +46932,7 @@
     </row>
     <row r="1861">
       <c r="A1861" t="n">
-        <v>4557273</v>
+        <v>4557080</v>
       </c>
       <c r="B1861" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
     </row>
     <row r="1862">
       <c r="A1862" t="n">
-        <v>4557276</v>
+        <v>4557084</v>
       </c>
       <c r="B1862" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
     </row>
     <row r="1863">
       <c r="A1863" t="n">
-        <v>4557279</v>
+        <v>4557085</v>
       </c>
       <c r="B1863" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
     </row>
     <row r="1864">
       <c r="A1864" t="n">
-        <v>4557282</v>
+        <v>4557095</v>
       </c>
       <c r="B1864" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
     </row>
     <row r="1865">
       <c r="A1865" t="n">
-        <v>4557292</v>
+        <v>4557098</v>
       </c>
       <c r="B1865" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
     </row>
     <row r="1866">
       <c r="A1866" t="n">
-        <v>4557299</v>
+        <v>4557105</v>
       </c>
       <c r="B1866" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
     </row>
     <row r="1867">
       <c r="A1867" t="n">
-        <v>4557302</v>
+        <v>4557111</v>
       </c>
       <c r="B1867" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
     </row>
     <row r="1868">
       <c r="A1868" t="n">
-        <v>4557311</v>
+        <v>4557121</v>
       </c>
       <c r="B1868" t="inlineStr">
         <is>
@@ -47132,7 +47132,7 @@
     </row>
     <row r="1869">
       <c r="A1869" t="n">
-        <v>4557318</v>
+        <v>4557131</v>
       </c>
       <c r="B1869" t="inlineStr">
         <is>
@@ -47157,7 +47157,7 @@
     </row>
     <row r="1870">
       <c r="A1870" t="n">
-        <v>4557322</v>
+        <v>4557132</v>
       </c>
       <c r="B1870" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
     </row>
     <row r="1871">
       <c r="A1871" t="n">
-        <v>4557328</v>
+        <v>4557135</v>
       </c>
       <c r="B1871" t="inlineStr">
         <is>
@@ -47207,7 +47207,7 @@
     </row>
     <row r="1872">
       <c r="A1872" t="n">
-        <v>4557329</v>
+        <v>4557138</v>
       </c>
       <c r="B1872" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
     </row>
     <row r="1873">
       <c r="A1873" t="n">
-        <v>4557331</v>
+        <v>4557142</v>
       </c>
       <c r="B1873" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
     </row>
     <row r="1874">
       <c r="A1874" t="n">
-        <v>4557341</v>
+        <v>4557143</v>
       </c>
       <c r="B1874" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
     </row>
     <row r="1875">
       <c r="A1875" t="n">
-        <v>4557344</v>
+        <v>4557146</v>
       </c>
       <c r="B1875" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
     </row>
     <row r="1876">
       <c r="A1876" t="n">
-        <v>4557346</v>
+        <v>4557154</v>
       </c>
       <c r="B1876" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
     </row>
     <row r="1877">
       <c r="A1877" t="n">
-        <v>4557356</v>
+        <v>4557158</v>
       </c>
       <c r="B1877" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
     </row>
     <row r="1878">
       <c r="A1878" t="n">
-        <v>4557365</v>
+        <v>4557175</v>
       </c>
       <c r="B1878" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
     </row>
     <row r="1879">
       <c r="A1879" t="n">
-        <v>4557366</v>
+        <v>4557191</v>
       </c>
       <c r="B1879" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
     </row>
     <row r="1880">
       <c r="A1880" t="n">
-        <v>4557367</v>
+        <v>4557192</v>
       </c>
       <c r="B1880" t="inlineStr">
         <is>
@@ -47432,7 +47432,7 @@
     </row>
     <row r="1881">
       <c r="A1881" t="n">
-        <v>4557370</v>
+        <v>4557196</v>
       </c>
       <c r="B1881" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
     </row>
     <row r="1882">
       <c r="A1882" t="n">
-        <v>4557380</v>
+        <v>4557204</v>
       </c>
       <c r="B1882" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
     </row>
     <row r="1883">
       <c r="A1883" t="n">
-        <v>4557382</v>
+        <v>4557208</v>
       </c>
       <c r="B1883" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
     </row>
     <row r="1884">
       <c r="A1884" t="n">
-        <v>4557384</v>
+        <v>4557212</v>
       </c>
       <c r="B1884" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
     </row>
     <row r="1885">
       <c r="A1885" t="n">
-        <v>4557389</v>
+        <v>4557221</v>
       </c>
       <c r="B1885" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
     </row>
     <row r="1886">
       <c r="A1886" t="n">
-        <v>4557391</v>
+        <v>4557231</v>
       </c>
       <c r="B1886" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
     </row>
     <row r="1887">
       <c r="A1887" t="n">
-        <v>4557398</v>
+        <v>4557240</v>
       </c>
       <c r="B1887" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
     </row>
     <row r="1888">
       <c r="A1888" t="n">
-        <v>4557405</v>
+        <v>4557243</v>
       </c>
       <c r="B1888" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
     </row>
     <row r="1889">
       <c r="A1889" t="n">
-        <v>4557408</v>
+        <v>4557252</v>
       </c>
       <c r="B1889" t="inlineStr">
         <is>
@@ -47657,7 +47657,7 @@
     </row>
     <row r="1890">
       <c r="A1890" t="n">
-        <v>4557421</v>
+        <v>4557271</v>
       </c>
       <c r="B1890" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
     </row>
     <row r="1891">
       <c r="A1891" t="n">
-        <v>4557431</v>
+        <v>4557273</v>
       </c>
       <c r="B1891" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
     </row>
     <row r="1892">
       <c r="A1892" t="n">
-        <v>4557436</v>
+        <v>4557276</v>
       </c>
       <c r="B1892" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
     </row>
     <row r="1893">
       <c r="A1893" t="n">
-        <v>4557442</v>
+        <v>4557279</v>
       </c>
       <c r="B1893" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
     </row>
     <row r="1894">
       <c r="A1894" t="n">
-        <v>4557443</v>
+        <v>4557282</v>
       </c>
       <c r="B1894" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
     </row>
     <row r="1895">
       <c r="A1895" t="n">
-        <v>4557453</v>
+        <v>4557292</v>
       </c>
       <c r="B1895" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
     </row>
     <row r="1896">
       <c r="A1896" t="n">
-        <v>4557460</v>
+        <v>4557299</v>
       </c>
       <c r="B1896" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
     </row>
     <row r="1897">
       <c r="A1897" t="n">
-        <v>4557463</v>
+        <v>4557302</v>
       </c>
       <c r="B1897" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
     </row>
     <row r="1898">
       <c r="A1898" t="n">
-        <v>4557470</v>
+        <v>4557311</v>
       </c>
       <c r="B1898" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
     </row>
     <row r="1899">
       <c r="A1899" t="n">
-        <v>4557473</v>
+        <v>4557318</v>
       </c>
       <c r="B1899" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
     </row>
     <row r="1900">
       <c r="A1900" t="n">
-        <v>4557478</v>
+        <v>4557322</v>
       </c>
       <c r="B1900" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
     </row>
     <row r="1901">
       <c r="A1901" t="n">
-        <v>4557480</v>
+        <v>4557328</v>
       </c>
       <c r="B1901" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
     </row>
     <row r="1902">
       <c r="A1902" t="n">
-        <v>4557483</v>
+        <v>4557329</v>
       </c>
       <c r="B1902" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
     </row>
     <row r="1903">
       <c r="A1903" t="n">
-        <v>4557490</v>
+        <v>4557331</v>
       </c>
       <c r="B1903" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
     </row>
     <row r="1904">
       <c r="A1904" t="n">
-        <v>4557493</v>
+        <v>4557341</v>
       </c>
       <c r="B1904" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
     </row>
     <row r="1905">
       <c r="A1905" t="n">
-        <v>4557498</v>
+        <v>4557344</v>
       </c>
       <c r="B1905" t="inlineStr">
         <is>
@@ -48057,7 +48057,7 @@
     </row>
     <row r="1906">
       <c r="A1906" t="n">
-        <v>4557507</v>
+        <v>4557346</v>
       </c>
       <c r="B1906" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
     </row>
     <row r="1907">
       <c r="A1907" t="n">
-        <v>4557512</v>
+        <v>4557356</v>
       </c>
       <c r="B1907" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
     </row>
     <row r="1908">
       <c r="A1908" t="n">
-        <v>4557522</v>
+        <v>4557365</v>
       </c>
       <c r="B1908" t="inlineStr">
         <is>
@@ -48132,7 +48132,7 @@
     </row>
     <row r="1909">
       <c r="A1909" t="n">
-        <v>4557527</v>
+        <v>4557366</v>
       </c>
       <c r="B1909" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
     </row>
     <row r="1910">
       <c r="A1910" t="n">
-        <v>4557530</v>
+        <v>4557367</v>
       </c>
       <c r="B1910" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
     </row>
     <row r="1911">
       <c r="A1911" t="n">
-        <v>4557538</v>
+        <v>4557370</v>
       </c>
       <c r="B1911" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
     </row>
     <row r="1912">
       <c r="A1912" t="n">
-        <v>4557548</v>
+        <v>4557380</v>
       </c>
       <c r="B1912" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
     </row>
     <row r="1913">
       <c r="A1913" t="n">
-        <v>4557555</v>
+        <v>4557382</v>
       </c>
       <c r="B1913" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
     </row>
     <row r="1914">
       <c r="A1914" t="n">
-        <v>4557559</v>
+        <v>4557384</v>
       </c>
       <c r="B1914" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
     </row>
     <row r="1915">
       <c r="A1915" t="n">
-        <v>4557564</v>
+        <v>4557389</v>
       </c>
       <c r="B1915" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
     </row>
     <row r="1916">
       <c r="A1916" t="n">
-        <v>4557568</v>
+        <v>4557391</v>
       </c>
       <c r="B1916" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
     </row>
     <row r="1917">
       <c r="A1917" t="n">
-        <v>4557578</v>
+        <v>4557398</v>
       </c>
       <c r="B1917" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
     </row>
     <row r="1918">
       <c r="A1918" t="n">
-        <v>4557594</v>
+        <v>4557405</v>
       </c>
       <c r="B1918" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
     </row>
     <row r="1919">
       <c r="A1919" t="n">
-        <v>4557597</v>
+        <v>4557408</v>
       </c>
       <c r="B1919" t="inlineStr">
         <is>
@@ -48407,7 +48407,7 @@
     </row>
     <row r="1920">
       <c r="A1920" t="n">
-        <v>4557598</v>
+        <v>4557421</v>
       </c>
       <c r="B1920" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
     </row>
     <row r="1921">
       <c r="A1921" t="n">
-        <v>4557603</v>
+        <v>4557431</v>
       </c>
       <c r="B1921" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
     </row>
     <row r="1922">
       <c r="A1922" t="n">
-        <v>4557612</v>
+        <v>4557436</v>
       </c>
       <c r="B1922" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
     </row>
     <row r="1923">
       <c r="A1923" t="n">
-        <v>4557620</v>
+        <v>4557442</v>
       </c>
       <c r="B1923" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
     </row>
     <row r="1924">
       <c r="A1924" t="n">
-        <v>4557627</v>
+        <v>4557443</v>
       </c>
       <c r="B1924" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
     </row>
     <row r="1925">
       <c r="A1925" t="n">
-        <v>4557631</v>
+        <v>4557453</v>
       </c>
       <c r="B1925" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
     </row>
     <row r="1926">
       <c r="A1926" t="n">
-        <v>4557640</v>
+        <v>4557460</v>
       </c>
       <c r="B1926" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
     </row>
     <row r="1927">
       <c r="A1927" t="n">
-        <v>4557646</v>
+        <v>4557463</v>
       </c>
       <c r="B1927" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
     </row>
     <row r="1928">
       <c r="A1928" t="n">
-        <v>4557649</v>
+        <v>4557470</v>
       </c>
       <c r="B1928" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
     </row>
     <row r="1929">
       <c r="A1929" t="n">
-        <v>4557663</v>
+        <v>4557473</v>
       </c>
       <c r="B1929" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
     </row>
     <row r="1930">
       <c r="A1930" t="n">
-        <v>4557665</v>
+        <v>4557478</v>
       </c>
       <c r="B1930" t="inlineStr">
         <is>
@@ -48682,7 +48682,7 @@
     </row>
     <row r="1931">
       <c r="A1931" t="n">
-        <v>4557668</v>
+        <v>4557480</v>
       </c>
       <c r="B1931" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
     </row>
     <row r="1932">
       <c r="A1932" t="n">
-        <v>4557672</v>
+        <v>4557483</v>
       </c>
       <c r="B1932" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
     </row>
     <row r="1933">
       <c r="A1933" t="n">
-        <v>4557682</v>
+        <v>4557490</v>
       </c>
       <c r="B1933" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
     </row>
     <row r="1934">
       <c r="A1934" t="n">
-        <v>4557697</v>
+        <v>4557493</v>
       </c>
       <c r="B1934" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
     </row>
     <row r="1935">
       <c r="A1935" t="n">
-        <v>4557702</v>
+        <v>4557498</v>
       </c>
       <c r="B1935" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
     </row>
     <row r="1936">
       <c r="A1936" t="n">
-        <v>4557708</v>
+        <v>4557507</v>
       </c>
       <c r="B1936" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
     </row>
     <row r="1937">
       <c r="A1937" t="n">
-        <v>4557716</v>
+        <v>4557512</v>
       </c>
       <c r="B1937" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
     </row>
     <row r="1938">
       <c r="A1938" t="n">
-        <v>4557719</v>
+        <v>4557522</v>
       </c>
       <c r="B1938" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
     </row>
     <row r="1939">
       <c r="A1939" t="n">
-        <v>4557729</v>
+        <v>4557527</v>
       </c>
       <c r="B1939" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
     </row>
     <row r="1940">
       <c r="A1940" t="n">
-        <v>4557738</v>
+        <v>4557530</v>
       </c>
       <c r="B1940" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
     </row>
     <row r="1941">
       <c r="A1941" t="n">
-        <v>4557740</v>
+        <v>4557538</v>
       </c>
       <c r="B1941" t="inlineStr">
         <is>
@@ -48957,7 +48957,7 @@
     </row>
     <row r="1942">
       <c r="A1942" t="n">
-        <v>4557747</v>
+        <v>4557548</v>
       </c>
       <c r="B1942" t="inlineStr">
         <is>
@@ -48982,7 +48982,7 @@
     </row>
     <row r="1943">
       <c r="A1943" t="n">
-        <v>4557804</v>
+        <v>4557555</v>
       </c>
       <c r="B1943" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
     </row>
     <row r="1944">
       <c r="A1944" t="n">
-        <v>4557810</v>
+        <v>4557559</v>
       </c>
       <c r="B1944" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
     </row>
     <row r="1945">
       <c r="A1945" t="n">
-        <v>4557826</v>
+        <v>4557564</v>
       </c>
       <c r="B1945" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
     </row>
     <row r="1946">
       <c r="A1946" t="n">
-        <v>4557832</v>
+        <v>4557568</v>
       </c>
       <c r="B1946" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
     </row>
     <row r="1947">
       <c r="A1947" t="n">
-        <v>4557843</v>
+        <v>4557578</v>
       </c>
       <c r="B1947" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
     </row>
     <row r="1948">
       <c r="A1948" t="n">
-        <v>4557851</v>
+        <v>4557594</v>
       </c>
       <c r="B1948" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
     </row>
     <row r="1949">
       <c r="A1949" t="n">
-        <v>4557856</v>
+        <v>4557597</v>
       </c>
       <c r="B1949" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
     </row>
     <row r="1950">
       <c r="A1950" t="n">
-        <v>4557866</v>
+        <v>4557598</v>
       </c>
       <c r="B1950" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
     </row>
     <row r="1951">
       <c r="A1951" t="n">
-        <v>4557869</v>
+        <v>4557603</v>
       </c>
       <c r="B1951" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
     </row>
     <row r="1952">
       <c r="A1952" t="n">
-        <v>4557870</v>
+        <v>4557612</v>
       </c>
       <c r="B1952" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
     </row>
     <row r="1953">
       <c r="A1953" t="n">
-        <v>4557874</v>
+        <v>4557620</v>
       </c>
       <c r="B1953" t="inlineStr">
         <is>
@@ -49257,7 +49257,7 @@
     </row>
     <row r="1954">
       <c r="A1954" t="n">
-        <v>4557877</v>
+        <v>4557627</v>
       </c>
       <c r="B1954" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
     </row>
     <row r="1955">
       <c r="A1955" t="n">
-        <v>4557883</v>
+        <v>4557631</v>
       </c>
       <c r="B1955" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
     </row>
     <row r="1956">
       <c r="A1956" t="n">
-        <v>4557889</v>
+        <v>4557640</v>
       </c>
       <c r="B1956" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
     </row>
     <row r="1957">
       <c r="A1957" t="n">
-        <v>4557895</v>
+        <v>4557646</v>
       </c>
       <c r="B1957" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
     </row>
     <row r="1958">
       <c r="A1958" t="n">
-        <v>4557901</v>
+        <v>4557649</v>
       </c>
       <c r="B1958" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
     </row>
     <row r="1959">
       <c r="A1959" t="n">
-        <v>4557906</v>
+        <v>4557663</v>
       </c>
       <c r="B1959" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
     </row>
     <row r="1960">
       <c r="A1960" t="n">
-        <v>4557911</v>
+        <v>4557665</v>
       </c>
       <c r="B1960" t="inlineStr">
         <is>
@@ -49432,7 +49432,7 @@
     </row>
     <row r="1961">
       <c r="A1961" t="n">
-        <v>4557916</v>
+        <v>4557668</v>
       </c>
       <c r="B1961" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
     </row>
     <row r="1962">
       <c r="A1962" t="n">
-        <v>4557921</v>
+        <v>4557672</v>
       </c>
       <c r="B1962" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
     </row>
     <row r="1963">
       <c r="A1963" t="n">
-        <v>4557928</v>
+        <v>4557682</v>
       </c>
       <c r="B1963" t="inlineStr">
         <is>
@@ -49507,7 +49507,7 @@
     </row>
     <row r="1964">
       <c r="A1964" t="n">
-        <v>4557932</v>
+        <v>4557697</v>
       </c>
       <c r="B1964" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
     </row>
     <row r="1965">
       <c r="A1965" t="n">
-        <v>4557935</v>
+        <v>4557702</v>
       </c>
       <c r="B1965" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
     </row>
     <row r="1966">
       <c r="A1966" t="n">
-        <v>4557940</v>
+        <v>4557708</v>
       </c>
       <c r="B1966" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
     </row>
     <row r="1967">
       <c r="A1967" t="n">
-        <v>4557950</v>
+        <v>4557716</v>
       </c>
       <c r="B1967" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
     </row>
     <row r="1968">
       <c r="A1968" t="n">
-        <v>4557958</v>
+        <v>4557719</v>
       </c>
       <c r="B1968" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
     </row>
     <row r="1969">
       <c r="A1969" t="n">
-        <v>4557966</v>
+        <v>4557729</v>
       </c>
       <c r="B1969" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
     </row>
     <row r="1970">
       <c r="A1970" t="n">
-        <v>4557974</v>
+        <v>4557738</v>
       </c>
       <c r="B1970" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
     </row>
     <row r="1971">
       <c r="A1971" t="n">
-        <v>4557976</v>
+        <v>4557740</v>
       </c>
       <c r="B1971" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
     </row>
     <row r="1972">
       <c r="A1972" t="n">
-        <v>4557983</v>
+        <v>4557747</v>
       </c>
       <c r="B1972" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
     </row>
     <row r="1973">
       <c r="A1973" t="n">
-        <v>4557990</v>
+        <v>4557757</v>
       </c>
       <c r="B1973" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
     </row>
     <row r="1974">
       <c r="A1974" t="n">
-        <v>4557999</v>
+        <v>4557761</v>
       </c>
       <c r="B1974" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
     </row>
     <row r="1975">
       <c r="A1975" t="n">
-        <v>4558009</v>
+        <v>4557768</v>
       </c>
       <c r="B1975" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
     </row>
     <row r="1976">
       <c r="A1976" t="n">
-        <v>4558020</v>
+        <v>4557780</v>
       </c>
       <c r="B1976" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
     </row>
     <row r="1977">
       <c r="A1977" t="n">
-        <v>4558027</v>
+        <v>4557804</v>
       </c>
       <c r="B1977" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
     </row>
     <row r="1978">
       <c r="A1978" t="n">
-        <v>4558029</v>
+        <v>4557810</v>
       </c>
       <c r="B1978" t="inlineStr">
         <is>
@@ -49882,7 +49882,7 @@
     </row>
     <row r="1979">
       <c r="A1979" t="n">
-        <v>4558030</v>
+        <v>4557826</v>
       </c>
       <c r="B1979" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
     </row>
     <row r="1980">
       <c r="A1980" t="n">
-        <v>4558038</v>
+        <v>4557832</v>
       </c>
       <c r="B1980" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
     </row>
     <row r="1981">
       <c r="A1981" t="n">
-        <v>4558043</v>
+        <v>4557843</v>
       </c>
       <c r="B1981" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
     </row>
     <row r="1982">
       <c r="A1982" t="n">
-        <v>4558046</v>
+        <v>4557851</v>
       </c>
       <c r="B1982" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
     </row>
     <row r="1983">
       <c r="A1983" t="n">
-        <v>4558050</v>
+        <v>4557856</v>
       </c>
       <c r="B1983" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
     </row>
     <row r="1984">
       <c r="A1984" t="n">
-        <v>4558055</v>
+        <v>4557866</v>
       </c>
       <c r="B1984" t="inlineStr">
         <is>
@@ -50032,7 +50032,7 @@
     </row>
     <row r="1985">
       <c r="A1985" t="n">
-        <v>4558058</v>
+        <v>4557869</v>
       </c>
       <c r="B1985" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
     </row>
     <row r="1986">
       <c r="A1986" t="n">
-        <v>4558061</v>
+        <v>4557870</v>
       </c>
       <c r="B1986" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
     </row>
     <row r="1987">
       <c r="A1987" t="n">
-        <v>4558064</v>
+        <v>4557874</v>
       </c>
       <c r="B1987" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
     </row>
     <row r="1988">
       <c r="A1988" t="n">
-        <v>4558067</v>
+        <v>4557877</v>
       </c>
       <c r="B1988" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
     </row>
     <row r="1989">
       <c r="A1989" t="n">
-        <v>4558075</v>
+        <v>4557883</v>
       </c>
       <c r="B1989" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
     </row>
     <row r="1990">
       <c r="A1990" t="n">
-        <v>4558082</v>
+        <v>4557889</v>
       </c>
       <c r="B1990" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
     </row>
     <row r="1991">
       <c r="A1991" t="n">
-        <v>4558092</v>
+        <v>4557895</v>
       </c>
       <c r="B1991" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
     </row>
     <row r="1992">
       <c r="A1992" t="n">
-        <v>4558095</v>
+        <v>4557901</v>
       </c>
       <c r="B1992" t="inlineStr">
         <is>
@@ -50232,7 +50232,7 @@
     </row>
     <row r="1993">
       <c r="A1993" t="n">
-        <v>4558096</v>
+        <v>4557906</v>
       </c>
       <c r="B1993" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
     </row>
     <row r="1994">
       <c r="A1994" t="n">
-        <v>4558097</v>
+        <v>4557911</v>
       </c>
       <c r="B1994" t="inlineStr">
         <is>
@@ -50282,7 +50282,7 @@
     </row>
     <row r="1995">
       <c r="A1995" t="n">
-        <v>4558098</v>
+        <v>4557916</v>
       </c>
       <c r="B1995" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
     </row>
     <row r="1996">
       <c r="A1996" t="n">
-        <v>4558108</v>
+        <v>4557921</v>
       </c>
       <c r="B1996" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
     </row>
     <row r="1997">
       <c r="A1997" t="n">
-        <v>4558114</v>
+        <v>4557928</v>
       </c>
       <c r="B1997" t="inlineStr">
         <is>
@@ -50357,7 +50357,7 @@
     </row>
     <row r="1998">
       <c r="A1998" t="n">
-        <v>4558119</v>
+        <v>4557784</v>
       </c>
       <c r="B1998" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
     </row>
     <row r="1999">
       <c r="A1999" t="n">
-        <v>4558120</v>
+        <v>4557790</v>
       </c>
       <c r="B1999" t="inlineStr">
         <is>
@@ -50407,7 +50407,7 @@
     </row>
     <row r="2000">
       <c r="A2000" t="n">
-        <v>4558121</v>
+        <v>4557795</v>
       </c>
       <c r="B2000" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
     </row>
     <row r="2001">
       <c r="A2001" t="n">
-        <v>4558122</v>
+        <v>4557797</v>
       </c>
       <c r="B2001" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
     </row>
     <row r="2002">
       <c r="A2002" t="n">
-        <v>4558130</v>
+        <v>4557932</v>
       </c>
       <c r="B2002" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
     </row>
     <row r="2003">
       <c r="A2003" t="n">
-        <v>4558140</v>
+        <v>4557935</v>
       </c>
       <c r="B2003" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
     </row>
     <row r="2004">
       <c r="A2004" t="n">
-        <v>4558147</v>
+        <v>4557940</v>
       </c>
       <c r="B2004" t="inlineStr">
         <is>
@@ -50532,7 +50532,7 @@
     </row>
     <row r="2005">
       <c r="A2005" t="n">
-        <v>4558154</v>
+        <v>4557950</v>
       </c>
       <c r="B2005" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
     </row>
     <row r="2006">
       <c r="A2006" t="n">
-        <v>4558161</v>
+        <v>4557958</v>
       </c>
       <c r="B2006" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
     </row>
     <row r="2007">
       <c r="A2007" t="n">
-        <v>4558164</v>
+        <v>4557966</v>
       </c>
       <c r="B2007" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
     </row>
     <row r="2008">
       <c r="A2008" t="n">
-        <v>4558171</v>
+        <v>4557974</v>
       </c>
       <c r="B2008" t="inlineStr">
         <is>
@@ -50632,7 +50632,7 @@
     </row>
     <row r="2009">
       <c r="A2009" t="n">
-        <v>4558173</v>
+        <v>4557976</v>
       </c>
       <c r="B2009" t="inlineStr">
         <is>
@@ -50657,7 +50657,7 @@
     </row>
     <row r="2010">
       <c r="A2010" t="n">
-        <v>4558180</v>
+        <v>4557983</v>
       </c>
       <c r="B2010" t="inlineStr">
         <is>
@@ -50682,7 +50682,7 @@
     </row>
     <row r="2011">
       <c r="A2011" t="n">
-        <v>4558184</v>
+        <v>4557990</v>
       </c>
       <c r="B2011" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
     </row>
     <row r="2012">
       <c r="A2012" t="n">
-        <v>4558192</v>
+        <v>4557999</v>
       </c>
       <c r="B2012" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
     </row>
     <row r="2013">
       <c r="A2013" t="n">
-        <v>4556027</v>
+        <v>4558009</v>
       </c>
       <c r="B2013" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
     </row>
     <row r="2014">
       <c r="A2014" t="n">
-        <v>4556044</v>
+        <v>4558020</v>
       </c>
       <c r="B2014" t="inlineStr">
         <is>
@@ -50782,7 +50782,7 @@
     </row>
     <row r="2015">
       <c r="A2015" t="n">
-        <v>4556057</v>
+        <v>4558027</v>
       </c>
       <c r="B2015" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
     </row>
     <row r="2016">
       <c r="A2016" t="n">
-        <v>4556064</v>
+        <v>4558029</v>
       </c>
       <c r="B2016" t="inlineStr">
         <is>
@@ -50832,7 +50832,7 @@
     </row>
     <row r="2017">
       <c r="A2017" t="n">
-        <v>4556071</v>
+        <v>4558030</v>
       </c>
       <c r="B2017" t="inlineStr">
         <is>
@@ -50857,7 +50857,7 @@
     </row>
     <row r="2018">
       <c r="A2018" t="n">
-        <v>4556081</v>
+        <v>4558038</v>
       </c>
       <c r="B2018" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
     </row>
     <row r="2019">
       <c r="A2019" t="n">
-        <v>4556087</v>
+        <v>4558043</v>
       </c>
       <c r="B2019" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
     </row>
     <row r="2020">
       <c r="A2020" t="n">
-        <v>4556088</v>
+        <v>4558046</v>
       </c>
       <c r="B2020" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
     </row>
     <row r="2021">
       <c r="A2021" t="n">
-        <v>4556096</v>
+        <v>4558050</v>
       </c>
       <c r="B2021" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
     </row>
     <row r="2022">
       <c r="A2022" t="n">
-        <v>4556100</v>
+        <v>4558055</v>
       </c>
       <c r="B2022" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
     </row>
     <row r="2023">
       <c r="A2023" t="n">
-        <v>4556106</v>
+        <v>4558058</v>
       </c>
       <c r="B2023" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
     </row>
     <row r="2024">
       <c r="A2024" t="n">
-        <v>4556116</v>
+        <v>4558061</v>
       </c>
       <c r="B2024" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
     </row>
     <row r="2025">
       <c r="A2025" t="n">
-        <v>4556122</v>
+        <v>4558064</v>
       </c>
       <c r="B2025" t="inlineStr">
         <is>
@@ -51057,7 +51057,7 @@
     </row>
     <row r="2026">
       <c r="A2026" t="n">
-        <v>4556123</v>
+        <v>4558067</v>
       </c>
       <c r="B2026" t="inlineStr">
         <is>
@@ -51082,7 +51082,7 @@
     </row>
     <row r="2027">
       <c r="A2027" t="n">
-        <v>4556126</v>
+        <v>4558075</v>
       </c>
       <c r="B2027" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
     </row>
     <row r="2028">
       <c r="A2028" t="n">
-        <v>4558204</v>
+        <v>4558082</v>
       </c>
       <c r="B2028" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
     </row>
     <row r="2029">
       <c r="A2029" t="n">
-        <v>4558213</v>
+        <v>4558092</v>
       </c>
       <c r="B2029" t="inlineStr">
         <is>
@@ -51157,7 +51157,7 @@
     </row>
     <row r="2030">
       <c r="A2030" t="n">
-        <v>4558216</v>
+        <v>4558095</v>
       </c>
       <c r="B2030" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
     </row>
     <row r="2031">
       <c r="A2031" t="n">
-        <v>4558221</v>
+        <v>4558096</v>
       </c>
       <c r="B2031" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
     </row>
     <row r="2032">
       <c r="A2032" t="n">
-        <v>4558223</v>
+        <v>4558097</v>
       </c>
       <c r="B2032" t="inlineStr">
         <is>
@@ -51232,7 +51232,7 @@
     </row>
     <row r="2033">
       <c r="A2033" t="n">
-        <v>4558228</v>
+        <v>4558098</v>
       </c>
       <c r="B2033" t="inlineStr">
         <is>
@@ -51257,7 +51257,7 @@
     </row>
     <row r="2034">
       <c r="A2034" t="n">
-        <v>4558238</v>
+        <v>4558108</v>
       </c>
       <c r="B2034" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
     </row>
     <row r="2035">
       <c r="A2035" t="n">
-        <v>4558248</v>
+        <v>4558114</v>
       </c>
       <c r="B2035" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
     </row>
     <row r="2036">
       <c r="A2036" t="n">
-        <v>4558253</v>
+        <v>4558119</v>
       </c>
       <c r="B2036" t="inlineStr">
         <is>
@@ -51332,7 +51332,7 @@
     </row>
     <row r="2037">
       <c r="A2037" t="n">
-        <v>4558254</v>
+        <v>4558120</v>
       </c>
       <c r="B2037" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
     </row>
     <row r="2038">
       <c r="A2038" t="n">
-        <v>4558259</v>
+        <v>4558121</v>
       </c>
       <c r="B2038" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
     </row>
     <row r="2039">
       <c r="A2039" t="n">
-        <v>4558277</v>
+        <v>4558122</v>
       </c>
       <c r="B2039" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
     </row>
     <row r="2040">
       <c r="A2040" t="n">
-        <v>4558287</v>
+        <v>4558130</v>
       </c>
       <c r="B2040" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
     </row>
     <row r="2041">
       <c r="A2041" t="n">
-        <v>4558293</v>
+        <v>4558140</v>
       </c>
       <c r="B2041" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
     </row>
     <row r="2042">
       <c r="A2042" t="n">
-        <v>4558297</v>
+        <v>4558147</v>
       </c>
       <c r="B2042" t="inlineStr">
         <is>
@@ -51482,7 +51482,7 @@
     </row>
     <row r="2043">
       <c r="A2043" t="n">
-        <v>4558302</v>
+        <v>4558154</v>
       </c>
       <c r="B2043" t="inlineStr">
         <is>
@@ -51507,7 +51507,7 @@
     </row>
     <row r="2044">
       <c r="A2044" t="n">
-        <v>4558310</v>
+        <v>4558161</v>
       </c>
       <c r="B2044" t="inlineStr">
         <is>
@@ -51532,7 +51532,7 @@
     </row>
     <row r="2045">
       <c r="A2045" t="n">
-        <v>4558317</v>
+        <v>4558164</v>
       </c>
       <c r="B2045" t="inlineStr">
         <is>
@@ -51557,7 +51557,7 @@
     </row>
     <row r="2046">
       <c r="A2046" t="n">
-        <v>4558318</v>
+        <v>4558171</v>
       </c>
       <c r="B2046" t="inlineStr">
         <is>
@@ -51582,7 +51582,7 @@
     </row>
     <row r="2047">
       <c r="A2047" t="n">
-        <v>4558322</v>
+        <v>4558173</v>
       </c>
       <c r="B2047" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
     </row>
     <row r="2048">
       <c r="A2048" t="n">
-        <v>4558326</v>
+        <v>4558180</v>
       </c>
       <c r="B2048" t="inlineStr">
         <is>
@@ -51632,7 +51632,7 @@
     </row>
     <row r="2049">
       <c r="A2049" t="n">
-        <v>4558330</v>
+        <v>4558184</v>
       </c>
       <c r="B2049" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
     </row>
     <row r="2050">
       <c r="A2050" t="n">
-        <v>4558331</v>
+        <v>4558192</v>
       </c>
       <c r="B2050" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
     </row>
     <row r="2051">
       <c r="A2051" t="n">
-        <v>4558335</v>
+        <v>4558204</v>
       </c>
       <c r="B2051" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
     </row>
     <row r="2052">
       <c r="A2052" t="n">
-        <v>4558338</v>
+        <v>4558213</v>
       </c>
       <c r="B2052" t="inlineStr">
         <is>
@@ -51732,7 +51732,7 @@
     </row>
     <row r="2053">
       <c r="A2053" t="n">
-        <v>4558348</v>
+        <v>4558216</v>
       </c>
       <c r="B2053" t="inlineStr">
         <is>
@@ -51757,7 +51757,7 @@
     </row>
     <row r="2054">
       <c r="A2054" t="n">
-        <v>4558354</v>
+        <v>4558221</v>
       </c>
       <c r="B2054" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
     </row>
     <row r="2055">
       <c r="A2055" t="n">
-        <v>4558362</v>
+        <v>4558223</v>
       </c>
       <c r="B2055" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
     </row>
     <row r="2056">
       <c r="A2056" t="n">
-        <v>4558369</v>
+        <v>4558228</v>
       </c>
       <c r="B2056" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
     </row>
     <row r="2057">
       <c r="A2057" t="n">
-        <v>4558375</v>
+        <v>4558238</v>
       </c>
       <c r="B2057" t="inlineStr">
         <is>
@@ -51857,7 +51857,7 @@
     </row>
     <row r="2058">
       <c r="A2058" t="n">
-        <v>4558376</v>
+        <v>4558248</v>
       </c>
       <c r="B2058" t="inlineStr">
         <is>
@@ -51882,7 +51882,7 @@
     </row>
     <row r="2059">
       <c r="A2059" t="n">
-        <v>4558379</v>
+        <v>4558253</v>
       </c>
       <c r="B2059" t="inlineStr">
         <is>
@@ -51907,7 +51907,7 @@
     </row>
     <row r="2060">
       <c r="A2060" t="n">
-        <v>4558381</v>
+        <v>4558254</v>
       </c>
       <c r="B2060" t="inlineStr">
         <is>
@@ -51932,7 +51932,7 @@
     </row>
     <row r="2061">
       <c r="A2061" t="n">
-        <v>4558383</v>
+        <v>4558259</v>
       </c>
       <c r="B2061" t="inlineStr">
         <is>
@@ -51957,576 +51957,751 @@
     </row>
     <row r="2062">
       <c r="A2062" t="n">
-        <v>4558362</v>
+        <v>4558277</v>
       </c>
       <c r="B2062" t="inlineStr">
         <is>
-          <t>T2051</t>
+          <t>NT6124</t>
         </is>
       </c>
       <c r="C2062" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2062" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2062" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2063">
       <c r="A2063" t="n">
-        <v>4558369</v>
+        <v>4558287</v>
       </c>
       <c r="B2063" t="inlineStr">
         <is>
-          <t>T2051</t>
+          <t>NT6124</t>
         </is>
       </c>
       <c r="C2063" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2063" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2063" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2064">
       <c r="A2064" t="n">
-        <v>4558375</v>
+        <v>4558293</v>
       </c>
       <c r="B2064" t="inlineStr">
         <is>
-          <t>T2051</t>
+          <t>NT6124</t>
         </is>
       </c>
       <c r="C2064" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2064" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2064" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2065">
       <c r="A2065" t="n">
-        <v>4558376</v>
+        <v>4558297</v>
       </c>
       <c r="B2065" t="inlineStr">
         <is>
-          <t>T2051</t>
+          <t>NT6124</t>
         </is>
       </c>
       <c r="C2065" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2065" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2065" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2066">
       <c r="A2066" t="n">
-        <v>4558379</v>
+        <v>4558302</v>
       </c>
       <c r="B2066" t="inlineStr">
         <is>
-          <t>T2051</t>
+          <t>NT6124</t>
         </is>
       </c>
       <c r="C2066" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2066" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2066" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2067">
       <c r="A2067" t="n">
-        <v>4558381</v>
+        <v>4558310</v>
       </c>
       <c r="B2067" t="inlineStr">
         <is>
-          <t>T2051</t>
+          <t>NT6124</t>
         </is>
       </c>
       <c r="C2067" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2067" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2067" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2068">
       <c r="A2068" t="n">
-        <v>4558383</v>
+        <v>4558317</v>
       </c>
       <c r="B2068" t="inlineStr">
         <is>
-          <t>T2051</t>
+          <t>NT6124</t>
         </is>
       </c>
       <c r="C2068" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2068" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2068" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2069">
       <c r="A2069" t="n">
-        <v>4556131</v>
+        <v>4558318</v>
       </c>
       <c r="B2069" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>NT6124</t>
         </is>
       </c>
       <c r="C2069" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2069" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2069" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2070">
       <c r="A2070" t="n">
-        <v>4556136</v>
+        <v>4558322</v>
       </c>
       <c r="B2070" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2070" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2070" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2070" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2071">
       <c r="A2071" t="n">
-        <v>4556142</v>
+        <v>4558326</v>
       </c>
       <c r="B2071" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2071" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2071" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2071" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2072">
       <c r="A2072" t="n">
-        <v>4556150</v>
+        <v>4558330</v>
       </c>
       <c r="B2072" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2072" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2072" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2072" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2073">
       <c r="A2073" t="n">
-        <v>4556155</v>
+        <v>4558331</v>
       </c>
       <c r="B2073" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2073" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2073" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2073" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2074">
       <c r="A2074" t="n">
-        <v>4556158</v>
+        <v>4558335</v>
       </c>
       <c r="B2074" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2074" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2074" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2074" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2075">
       <c r="A2075" t="n">
-        <v>4556170</v>
+        <v>4558338</v>
       </c>
       <c r="B2075" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2075" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2075" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2075" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2076">
       <c r="A2076" t="n">
-        <v>4556174</v>
+        <v>4558348</v>
       </c>
       <c r="B2076" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2076" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2076" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2076" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2077">
       <c r="A2077" t="n">
-        <v>4556180</v>
+        <v>4558354</v>
       </c>
       <c r="B2077" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2077" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2077" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2077" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2078">
       <c r="A2078" t="n">
-        <v>4556182</v>
+        <v>4558362</v>
       </c>
       <c r="B2078" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2078" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2078" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2078" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2079">
       <c r="A2079" t="n">
-        <v>4556186</v>
+        <v>4558369</v>
       </c>
       <c r="B2079" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2079" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2079" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2079" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2080">
       <c r="A2080" t="n">
-        <v>4556192</v>
+        <v>4558375</v>
       </c>
       <c r="B2080" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2080" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2080" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2080" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2081">
       <c r="A2081" t="n">
-        <v>4556198</v>
+        <v>4558376</v>
       </c>
       <c r="B2081" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2081" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2081" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2081" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2082">
       <c r="A2082" t="n">
-        <v>4556202</v>
+        <v>4558379</v>
       </c>
       <c r="B2082" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2082" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2082" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2082" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2083">
       <c r="A2083" t="n">
-        <v>4556210</v>
+        <v>4558381</v>
       </c>
       <c r="B2083" t="inlineStr">
         <is>
-          <t>NT6090</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2083" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2083" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2083" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
     </row>
     <row r="2084">
       <c r="A2084" t="n">
-        <v>4557757</v>
+        <v>4558383</v>
       </c>
       <c r="B2084" t="inlineStr">
         <is>
-          <t>TT 4251</t>
+          <t>T2068</t>
         </is>
       </c>
       <c r="C2084" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2084" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2084" t="inlineStr">
         <is>
-          <t>18/01/2026</t>
+          <t>16/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="n">
+        <v>4558362</v>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>T2051</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D2085" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="n">
+        <v>4558369</v>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>T2051</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D2086" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="n">
+        <v>4558375</v>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>T2051</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D2087" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="n">
+        <v>4558376</v>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>T2051</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D2088" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="n">
+        <v>4558379</v>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>T2051</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D2089" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="n">
+        <v>4558381</v>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>T2051</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D2090" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="n">
+        <v>4558383</v>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>T2051</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D2091" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>17/01/2026</t>
         </is>
       </c>
     </row>

--- a/Result/AsignacionTurnos.xlsx
+++ b/Result/AsignacionTurnos.xlsx
@@ -429,12 +429,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Inicio</t>
+          <t>Hora_Inicio</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hora_Termino</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
